--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -5,21 +5,20 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnthonyPenzes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AnthonyPenzes\Desktop\RMAA System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFF7078-F038-4FC2-AE61-1AE425A557D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2928416C-AE14-4972-872D-5051547EA2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27195" yWindow="1665" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$I$44</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="50">
   <si>
     <t>Name of Client:</t>
   </si>
@@ -97,9 +96,6 @@
   </si>
   <si>
     <t>Slaughter Technique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service Cost </t>
   </si>
   <si>
     <t xml:space="preserve">General Manager : Dr GC Neethling
@@ -108,9 +104,6 @@
   </si>
   <si>
     <t xml:space="preserve"> TOTAL Excl 15% VAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discounted </t>
   </si>
   <si>
     <t>012 349 1237</t>
@@ -208,21 +201,9 @@
     <t>Conducting audit verification &amp; sampling enables us to provide you with a discount.</t>
   </si>
   <si>
-    <t>Skills Program</t>
-  </si>
-  <si>
     <t>Training and Support Services Contract 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Membership </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verification Audit </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sampling </t>
-  </si>
-  <si>
     <t>Doornplaat Abattoir</t>
   </si>
   <si>
@@ -257,20 +238,25 @@
   </si>
   <si>
     <t>QUOTATION DATE: 23/02/2026</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Discounted</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-1C09]dd\ mmmm\ yyyy;@"/>
     <numFmt numFmtId="166" formatCode="[$R-1C09]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="168" formatCode="&quot;R&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="_-[$R-1C09]* #,##0.00_-;\-[$R-1C09]* #,##0.00_-;_-[$R-1C09]* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="173" formatCode="#,##0\K"/>
+    <numFmt numFmtId="171" formatCode="0\ &quot;km&quot;"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -472,7 +458,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -784,7 +770,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -794,7 +780,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -811,20 +830,122 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -835,14 +956,81 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -851,101 +1039,42 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -957,7 +1086,7 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -989,34 +1118,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1026,146 +1134,145 @@
     <xf numFmtId="166" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="20" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1177,164 +1284,287 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="173" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1367,13 +1597,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>97291</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>46377</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>297656</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>639103</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1531,13 +1761,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>98880</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>32945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>2211</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>659475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1870,16 +2100,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA42"/>
+  <dimension ref="A1:AA44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="3" width="21.5703125" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="16" customWidth="1"/>
     <col min="6" max="6" width="12.28515625" customWidth="1"/>
     <col min="7" max="8" width="10.5703125" customWidth="1"/>
-    <col min="9" max="9" width="11" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1887,713 +2117,722 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="19"/>
+      <c r="E1" s="14"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="19"/>
+      <c r="I1" s="14"/>
     </row>
     <row r="2" spans="1:9" s="5" customFormat="1" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="110" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="105" t="s">
+      <c r="A2" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="36"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="38"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="39" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="41"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89" t="s">
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="38"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="45"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="50"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="50"/>
+    </row>
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="49"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="50"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="106"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="95"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="83" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="107" t="s">
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
+      <c r="I12" s="50"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="61" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="109"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="84"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="94" t="s">
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="95"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="85" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="111" t="s">
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="38"/>
+    </row>
+    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="112"/>
-      <c r="F7" s="112"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="113"/>
-    </row>
-    <row r="8" spans="1:9" ht="14.45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="83" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="84"/>
-      <c r="C8" s="84"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="95"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="101" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="102"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="83" t="s">
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="33"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="59" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="60"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="101" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="102"/>
-    </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="102"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="83" t="s">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="84"/>
-      <c r="C12" s="84"/>
-      <c r="D12" s="101" t="s">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="38"/>
+    </row>
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="65"/>
+    </row>
+    <row r="20" spans="1:11" s="2" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="56"/>
+    </row>
+    <row r="21" spans="1:11" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="104" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="105"/>
+      <c r="C21" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="102"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="96" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="97"/>
-      <c r="C13" s="97"/>
-      <c r="D13" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="115"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="115"/>
-      <c r="I13" s="116"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="94" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94"/>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="95"/>
-    </row>
-    <row r="15" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="90" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="91"/>
-      <c r="C15" s="91"/>
-      <c r="D15" s="103" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="89"/>
-      <c r="C16" s="89"/>
-      <c r="D16" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="92"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="93"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="83" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="95"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="84"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="94" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="95"/>
-    </row>
-    <row r="19" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="90" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="91"/>
-      <c r="C19" s="91"/>
-      <c r="D19" s="98" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="99"/>
-      <c r="I19" s="100"/>
-    </row>
-    <row r="20" spans="1:27" s="2" customFormat="1" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="126" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="127"/>
-      <c r="C20" s="127"/>
-      <c r="D20" s="127"/>
-      <c r="E20" s="127"/>
-      <c r="F20" s="127"/>
-      <c r="G20" s="127"/>
-      <c r="H20" s="127"/>
-      <c r="I20" s="128"/>
-    </row>
-    <row r="21" spans="1:27" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="120" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="121"/>
-      <c r="C21" s="122" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="122" t="s">
+      <c r="E21" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="E21" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="122" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="124" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" s="125" t="s">
+      <c r="F21" s="75" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="106" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="107" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="I21" s="129"/>
-      <c r="J21" s="130"/>
-    </row>
-    <row r="22" spans="1:27" s="6" customFormat="1" ht="25.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="86"/>
+      <c r="K21" s="84"/>
+    </row>
+    <row r="22" spans="1:11" s="6" customFormat="1" ht="25.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>1</v>
       </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="117"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="119">
-        <f>SUM(E22+(F22*5.5)+G22)</f>
+      <c r="B22" s="72"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="27">
+        <f>SUM(F22+(G22*5.5)+H22)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="118"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:27" s="6" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="87"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" s="6" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>2</v>
       </c>
-      <c r="B23" s="46"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="119">
-        <f>SUM(E23+(F23*5.5)+G23)</f>
+      <c r="B23" s="72"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="27">
+        <f>SUM(F23+(G23*5.5)+H23)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="118"/>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:27" s="6" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="87"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" s="6" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>3</v>
       </c>
-      <c r="B24" s="46"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="119">
-        <f>SUM(E24+(F24*5.5)+G24)</f>
+      <c r="B24" s="72"/>
+      <c r="C24" s="78"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="78"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="27">
+        <f>SUM(F24+(G24*5.5)+H24)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="131"/>
-      <c r="J24" s="132"/>
-    </row>
-    <row r="25" spans="1:27" s="6" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="57"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="59"/>
+      <c r="J24" s="87"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="1:11" s="6" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7">
+        <v>4</v>
+      </c>
+      <c r="B25" s="72"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="27">
+        <f>SUM(F25+(G25*5.5)+H25)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="87"/>
       <c r="K25" s="10"/>
     </row>
-    <row r="26" spans="1:27" s="6" customFormat="1" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="7">
+    <row r="26" spans="1:11" s="6" customFormat="1" ht="21.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="108">
+        <v>5</v>
+      </c>
+      <c r="B26" s="109"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="83">
+        <f>SUM(F26+(G26*5.5)+H26)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="87"/>
+      <c r="K26" s="85"/>
+    </row>
+    <row r="27" spans="1:11" s="6" customFormat="1" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="102"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="73"/>
+      <c r="D27" s="73"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="103"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="1:11" s="6" customFormat="1" ht="21.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="112">
         <v>4</v>
       </c>
-      <c r="B26" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="67"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="44" t="str">
-        <f>F26&amp;"km"</f>
-        <v>km</v>
-      </c>
-      <c r="H26" s="34"/>
-      <c r="I26" s="33">
-        <f>SUM(E26+(F26*5.5)+H26)</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="10"/>
-    </row>
-    <row r="27" spans="1:27" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="30">
-        <v>4</v>
-      </c>
-      <c r="B27" s="60" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="35">
-        <v>2900</v>
-      </c>
-      <c r="F27" s="31"/>
-      <c r="G27" s="44" t="str">
-        <f t="shared" ref="G27" si="0">F27&amp;"km"</f>
-        <v>km</v>
-      </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="33">
-        <f>SUM(E27+(F27*5.5)+H27)</f>
-        <v>2900</v>
-      </c>
-      <c r="K27" s="10"/>
-    </row>
-    <row r="28" spans="1:27" s="6" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="7">
-        <v>5</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="36">
-        <v>3328.5</v>
-      </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="44" t="str">
+      <c r="B28" s="113" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="114"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="117"/>
+      <c r="G28" s="118" t="str">
         <f>F28&amp;"km"</f>
         <v>km</v>
       </c>
-      <c r="H28" s="27"/>
-      <c r="I28" s="33">
+      <c r="H28" s="117"/>
+      <c r="I28" s="119">
         <f>SUM(E28+(F28*5.5)+H28)</f>
-        <v>3328.5</v>
+        <v>0</v>
       </c>
       <c r="K28" s="10"/>
     </row>
-    <row r="29" spans="1:27" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="80" t="s">
+    <row r="29" spans="1:11" s="6" customFormat="1" ht="20.45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="124">
+        <v>4</v>
+      </c>
+      <c r="B29" s="125" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="126"/>
+      <c r="D29" s="126"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="128"/>
+      <c r="G29" s="129"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="131">
+        <f>SUM(F29+(G29*5.5)+H29)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="1:11" s="6" customFormat="1" ht="19.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="108">
+        <v>5</v>
+      </c>
+      <c r="B30" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="133"/>
+      <c r="D30" s="133"/>
+      <c r="E30" s="134"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="137"/>
+      <c r="I30" s="138">
+        <f>SUM(F30+(G30*5.5)+H30)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" spans="1:11" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="121"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="121"/>
+      <c r="H31" s="122"/>
+      <c r="I31" s="123">
+        <f>SUM(I22:I30)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" spans="1:11" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="7"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="17"/>
+      <c r="K32" s="10"/>
+    </row>
+    <row r="33" spans="1:27" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="112"/>
+      <c r="B33" s="139"/>
+      <c r="C33" s="140"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="143"/>
+      <c r="G33" s="143"/>
+      <c r="H33" s="144"/>
+      <c r="I33" s="145"/>
+      <c r="K33" s="10"/>
+    </row>
+    <row r="34" spans="1:27" s="20" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="150" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="151"/>
+      <c r="C34" s="152" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="153"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="155"/>
+      <c r="G34" s="156"/>
+      <c r="H34" s="157"/>
+      <c r="I34" s="158">
+        <f>SUM(F34+(G34*5.5)+H34)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="19"/>
+      <c r="M34" s="19"/>
+      <c r="N34" s="19"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="19"/>
+      <c r="Q34" s="19"/>
+      <c r="R34" s="19"/>
+      <c r="S34" s="19"/>
+      <c r="T34" s="19"/>
+      <c r="U34" s="19"/>
+      <c r="V34" s="19"/>
+      <c r="W34" s="19"/>
+      <c r="X34" s="19"/>
+      <c r="Y34" s="19"/>
+      <c r="Z34" s="19"/>
+      <c r="AA34" s="19"/>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" s="66"/>
+      <c r="B35" s="94"/>
+      <c r="C35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="100"/>
+      <c r="E35" s="101"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="99"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="18">
+        <f t="shared" ref="I35:I37" si="0">SUM(F35+(G35*5.5)+H35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36" s="66"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="100"/>
+      <c r="E36" s="101"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="159"/>
+      <c r="B37" s="160"/>
+      <c r="C37" s="161" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="162"/>
+      <c r="E37" s="163"/>
+      <c r="F37" s="164"/>
+      <c r="G37" s="165"/>
+      <c r="H37" s="166"/>
+      <c r="I37" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="146" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="147"/>
+      <c r="C38" s="147"/>
+      <c r="D38" s="147"/>
+      <c r="E38" s="147"/>
+      <c r="F38" s="147"/>
+      <c r="G38" s="147"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="149">
+        <f>SUM(I34:I37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="92"/>
+      <c r="C39" s="92"/>
+      <c r="D39" s="92"/>
+      <c r="E39" s="92"/>
+      <c r="F39" s="92"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="21">
+        <f>I31-I38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="81"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="82"/>
-      <c r="I29" s="26">
-        <f>SUM(I22:I28)</f>
-        <v>6228.5</v>
-      </c>
-      <c r="K29" s="10"/>
-    </row>
-    <row r="30" spans="1:27" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="24"/>
-      <c r="K30" s="10"/>
-    </row>
-    <row r="31" spans="1:27" s="6" customFormat="1" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="24"/>
-      <c r="K31" s="10"/>
-    </row>
-    <row r="32" spans="1:27" s="29" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="49" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="22">
-        <v>0</v>
-      </c>
-      <c r="F32" s="47">
-        <v>0</v>
-      </c>
-      <c r="G32" s="15" t="str">
-        <f>F32&amp;"km"</f>
-        <v>0km</v>
-      </c>
-      <c r="H32" s="48"/>
-      <c r="I32" s="25">
-        <f>SUM(E32+(F32*5.5)+H32)</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
-      <c r="AA32" s="28"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="51"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="22">
-        <v>2900</v>
-      </c>
-      <c r="F33" s="47">
-        <v>0</v>
-      </c>
-      <c r="G33" s="15" t="str">
-        <f>F33&amp;"km"</f>
-        <v>0km</v>
-      </c>
-      <c r="H33" s="4"/>
-      <c r="I33" s="25">
-        <f t="shared" ref="I33:I35" si="1">SUM(E33+(F33*5.5)+H33)</f>
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="51"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="22">
-        <v>3328.5</v>
-      </c>
-      <c r="F34" s="47">
-        <v>0</v>
-      </c>
-      <c r="G34" s="15" t="str">
-        <f>F34&amp;"km"</f>
-        <v>0km</v>
-      </c>
-      <c r="H34" s="45"/>
-      <c r="I34" s="25">
-        <f t="shared" si="1"/>
-        <v>3328.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="53"/>
-      <c r="B35" s="54"/>
-      <c r="C35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E35" s="22">
-        <v>0</v>
-      </c>
-      <c r="F35" s="47">
-        <v>0</v>
-      </c>
-      <c r="G35" s="15" t="str">
-        <f>F35&amp;"km"</f>
-        <v>0km</v>
-      </c>
-      <c r="H35" s="4"/>
-      <c r="I35" s="25">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="5" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="38">
-        <f>SUM(I32:I35)</f>
-        <v>6228.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="5" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="72"/>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="72"/>
-      <c r="G37" s="72"/>
-      <c r="H37" s="72"/>
-      <c r="I37" s="39">
-        <f>I29-I36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="74"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="74"/>
-      <c r="I38" s="75"/>
-    </row>
-    <row r="39" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="40"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="78"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="79"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="40"/>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="89"/>
+      <c r="C40" s="89"/>
+      <c r="D40" s="89"/>
+      <c r="E40" s="89"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="90"/>
+    </row>
+    <row r="41" spans="1:27" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="22"/>
+      <c r="B41" s="70"/>
+      <c r="C41" s="70"/>
+      <c r="D41" s="95"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="71"/>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A42" s="22"/>
+      <c r="B42" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="41"/>
-      <c r="H40" s="76" t="s">
+      <c r="C42" s="97"/>
+      <c r="D42" s="95"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="95"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="I40" s="77"/>
-    </row>
-    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="42"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="43"/>
-    </row>
-    <row r="42" spans="1:9" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
+      <c r="I42" s="69"/>
+    </row>
+    <row r="43" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="23"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="24"/>
+    </row>
+    <row r="44" spans="1:27" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="67"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="67"/>
+      <c r="I44" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="55">
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A34:B37"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D8:I8"/>
@@ -2607,6 +2846,19 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D2:I2"/>
     <mergeCell ref="A20:I20"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A17:C17"/>
@@ -2614,28 +2866,10 @@
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="D17:I17"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A13:C13"/>
     <mergeCell ref="D18:I18"/>
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D9:I9"/>
     <mergeCell ref="D10:I10"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A32:B35"/>
-    <mergeCell ref="A42:I42"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A38:I38"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="H21:I21"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <hyperlinks>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="168" formatCode="0\ &quot;km&quot;"/>
     <numFmt numFmtId="169" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -244,6 +244,12 @@
       <color rgb="FF0070C0"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -990,7 +996,7 @@
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1649,6 +1655,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2770,7 +2779,7 @@
       <c r="K33" s="85" t="n"/>
     </row>
     <row r="34" ht="16.5" customFormat="1" customHeight="1" s="218">
-      <c r="A34" s="219" t="inlineStr">
+      <c r="A34" s="242" t="inlineStr">
         <is>
           <t>Conducting an audit verification &amp; sampling enables us to provide you with a discount.</t>
         </is>
@@ -2977,8 +2986,8 @@
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:C2"/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -2902,7 +2902,7 @@
       <c r="G39" s="180" t="n"/>
       <c r="H39" s="236" t="n"/>
       <c r="I39" s="237">
-        <f>I31-I38</f>
+        <f>I31+I38</f>
         <v/>
       </c>
     </row>
@@ -2986,9 +2986,9 @@
     <mergeCell ref="H41:I41"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D36:E36"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D16:I16"/>
+    <mergeCell ref="D36:E36"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="B28:D28"/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -2573,7 +2573,7 @@
       </c>
       <c r="B22" s="72" t="n"/>
       <c r="C22" s="78" t="n"/>
-      <c r="D22" s="77" t="n"/>
+      <c r="D22" s="186" t="n"/>
       <c r="E22" s="78" t="n"/>
       <c r="F22" s="186" t="n"/>
       <c r="G22" s="187" t="n"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B23" s="72" t="n"/>
       <c r="C23" s="78" t="n"/>
-      <c r="D23" s="79" t="n"/>
+      <c r="D23" s="186" t="n"/>
       <c r="E23" s="78" t="n"/>
       <c r="F23" s="186" t="n"/>
       <c r="G23" s="187" t="n"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B24" s="72" t="n"/>
       <c r="C24" s="78" t="n"/>
-      <c r="D24" s="79" t="n"/>
+      <c r="D24" s="186" t="n"/>
       <c r="E24" s="78" t="n"/>
       <c r="F24" s="186" t="n"/>
       <c r="G24" s="187" t="n"/>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B25" s="72" t="n"/>
       <c r="C25" s="78" t="n"/>
-      <c r="D25" s="79" t="n"/>
+      <c r="D25" s="186" t="n"/>
       <c r="E25" s="78" t="n"/>
       <c r="F25" s="186" t="n"/>
       <c r="G25" s="187" t="n"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B26" s="109" t="n"/>
       <c r="C26" s="80" t="n"/>
-      <c r="D26" s="81" t="n"/>
+      <c r="D26" s="190" t="n"/>
       <c r="E26" s="80" t="n"/>
       <c r="F26" s="190" t="n"/>
       <c r="G26" s="191" t="n"/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -2579,7 +2579,7 @@
       <c r="G22" s="187" t="n"/>
       <c r="H22" s="188" t="n"/>
       <c r="I22" s="186">
-        <f>SUM(F22+(G22*5.5)+H22)</f>
+        <f>SUM(D22+F22+(G22*5.5)+H22)</f>
         <v/>
       </c>
       <c r="J22" s="189" t="n"/>
@@ -2597,7 +2597,7 @@
       <c r="G23" s="187" t="n"/>
       <c r="H23" s="188" t="n"/>
       <c r="I23" s="186">
-        <f>SUM(F23+(G23*5.5)+H23)</f>
+        <f>SUM(D23+F23+(G23*5.5)+H23)</f>
         <v/>
       </c>
       <c r="J23" s="189" t="n"/>
@@ -2615,7 +2615,7 @@
       <c r="G24" s="187" t="n"/>
       <c r="H24" s="188" t="n"/>
       <c r="I24" s="186">
-        <f>SUM(F24+(G24*5.5)+H24)</f>
+        <f>SUM(D24+F24+(G24*5.5)+H24)</f>
         <v/>
       </c>
       <c r="J24" s="189" t="n"/>
@@ -2633,7 +2633,7 @@
       <c r="G25" s="187" t="n"/>
       <c r="H25" s="188" t="n"/>
       <c r="I25" s="186">
-        <f>SUM(F25+(G25*5.5)+H25)</f>
+        <f>SUM(D25+F25+(G25*5.5)+H25)</f>
         <v/>
       </c>
       <c r="J25" s="189" t="n"/>
@@ -2651,7 +2651,7 @@
       <c r="G26" s="191" t="n"/>
       <c r="H26" s="192" t="n"/>
       <c r="I26" s="190">
-        <f>SUM(F26+(G26*5.5)+H26)</f>
+        <f>SUM(D26+F26+(G26*5.5)+H26)</f>
         <v/>
       </c>
       <c r="J26" s="189" t="n"/>
@@ -2796,7 +2796,7 @@
       <c r="G34" s="222" t="n"/>
       <c r="H34" s="223" t="n"/>
       <c r="I34" s="224">
-        <f>SUM(F34+(G34*5.5)+H34)</f>
+        <f>SUM(D34+F34+(G34*5.5)+H34)</f>
         <v/>
       </c>
       <c r="J34" s="189" t="n"/>
@@ -2831,7 +2831,7 @@
       <c r="G35" s="227" t="n"/>
       <c r="H35" s="226" t="n"/>
       <c r="I35" s="228">
-        <f>SUM(F35+(G35*5.5)+H35)</f>
+        <f>SUM(D35+F35+(G35*5.5)+H35)</f>
         <v/>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       <c r="G36" s="227" t="n"/>
       <c r="H36" s="226" t="n"/>
       <c r="I36" s="228">
-        <f>SUM(F36+(G36*5.5)+H36)</f>
+        <f>SUM(D36+F36+(G36*5.5)+H36)</f>
         <v/>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       <c r="G37" s="231" t="n"/>
       <c r="H37" s="230" t="n"/>
       <c r="I37" s="232">
-        <f>SUM(F37+(G37*5.5)+H37)</f>
+        <f>SUM(D37+F37+(G37*5.5)+H37)</f>
         <v/>
       </c>
     </row>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -2147,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA44"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" style="95" min="1" max="1"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="B23" s="72" t="n"/>
       <c r="C23" s="78" t="n"/>
-      <c r="D23" s="186" t="n"/>
+      <c r="D23" s="79" t="n"/>
       <c r="E23" s="78" t="n"/>
       <c r="F23" s="186" t="n"/>
       <c r="G23" s="187" t="n"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B24" s="72" t="n"/>
       <c r="C24" s="78" t="n"/>
-      <c r="D24" s="186" t="n"/>
+      <c r="D24" s="79" t="n"/>
       <c r="E24" s="78" t="n"/>
       <c r="F24" s="186" t="n"/>
       <c r="G24" s="187" t="n"/>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B25" s="72" t="n"/>
       <c r="C25" s="78" t="n"/>
-      <c r="D25" s="186" t="n"/>
+      <c r="D25" s="79" t="n"/>
       <c r="E25" s="78" t="n"/>
       <c r="F25" s="186" t="n"/>
       <c r="G25" s="187" t="n"/>
@@ -2657,223 +2657,214 @@
       <c r="J26" s="189" t="n"/>
       <c r="K26" s="85" t="n"/>
     </row>
-    <row r="27" ht="14.45" customFormat="1" customHeight="1" s="84" thickBot="1">
-      <c r="A27" s="193" t="n"/>
-      <c r="B27" s="194" t="n"/>
-      <c r="C27" s="194" t="n"/>
-      <c r="D27" s="194" t="n"/>
-      <c r="E27" s="194" t="n"/>
-      <c r="F27" s="194" t="n"/>
-      <c r="G27" s="194" t="n"/>
-      <c r="H27" s="194" t="n"/>
-      <c r="I27" s="195" t="n"/>
+    <row r="27" customFormat="1" s="84">
+      <c r="A27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="72" t="n"/>
+      <c r="C27" s="78" t="n"/>
+      <c r="D27" s="79" t="n"/>
+      <c r="E27" s="78" t="n"/>
+      <c r="F27" s="186" t="n"/>
+      <c r="G27" s="187" t="n"/>
+      <c r="H27" s="188" t="n"/>
+      <c r="I27" s="186">
+        <f>SUM(D27+F27+(G27*5.5)+H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="189" t="n"/>
       <c r="K27" s="85" t="n"/>
     </row>
-    <row r="28" hidden="1" ht="21.6" customFormat="1" customHeight="1" s="84">
-      <c r="A28" s="112" t="n">
+    <row r="28" customFormat="1" s="84">
+      <c r="A28" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="72" t="n"/>
+      <c r="C28" s="78" t="n"/>
+      <c r="D28" s="79" t="n"/>
+      <c r="E28" s="78" t="n"/>
+      <c r="F28" s="186" t="n"/>
+      <c r="G28" s="187" t="n"/>
+      <c r="H28" s="188" t="n"/>
+      <c r="I28" s="186">
+        <f>SUM(D28+F28+(G28*5.5)+H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="189" t="n"/>
+      <c r="K28" s="85" t="n"/>
+    </row>
+    <row r="29" customFormat="1" s="84">
+      <c r="A29" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="72" t="n"/>
+      <c r="C29" s="78" t="n"/>
+      <c r="D29" s="79" t="n"/>
+      <c r="E29" s="78" t="n"/>
+      <c r="F29" s="186" t="n"/>
+      <c r="G29" s="187" t="n"/>
+      <c r="H29" s="188" t="n"/>
+      <c r="I29" s="186">
+        <f>SUM(D29+F29+(G29*5.5)+H29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="189" t="n"/>
+      <c r="K29" s="85" t="n"/>
+    </row>
+    <row r="30" customFormat="1" s="84">
+      <c r="A30" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B30" s="72" t="n"/>
+      <c r="C30" s="78" t="n"/>
+      <c r="D30" s="79" t="n"/>
+      <c r="E30" s="78" t="n"/>
+      <c r="F30" s="186" t="n"/>
+      <c r="G30" s="187" t="n"/>
+      <c r="H30" s="188" t="n"/>
+      <c r="I30" s="186">
+        <f>SUM(D30+F30+(G30*5.5)+H30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="189" t="n"/>
+      <c r="K30" s="85" t="n"/>
+    </row>
+    <row r="31" customFormat="1" s="84">
+      <c r="A31" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" s="72" t="n"/>
+      <c r="C31" s="78" t="n"/>
+      <c r="D31" s="79" t="n"/>
+      <c r="E31" s="78" t="n"/>
+      <c r="F31" s="186" t="n"/>
+      <c r="G31" s="187" t="n"/>
+      <c r="H31" s="188" t="n"/>
+      <c r="I31" s="186">
+        <f>SUM(D31+F31+(G31*5.5)+H31)</f>
+        <v/>
+      </c>
+      <c r="J31" s="189" t="n"/>
+      <c r="K31" s="85" t="n"/>
+    </row>
+    <row r="32" customFormat="1" s="84">
+      <c r="A32" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B32" s="72" t="n"/>
+      <c r="C32" s="78" t="n"/>
+      <c r="D32" s="79" t="n"/>
+      <c r="E32" s="78" t="n"/>
+      <c r="F32" s="186" t="n"/>
+      <c r="G32" s="187" t="n"/>
+      <c r="H32" s="188" t="n"/>
+      <c r="I32" s="186">
+        <f>SUM(D32+F32+(G32*5.5)+H32)</f>
+        <v/>
+      </c>
+      <c r="J32" s="189" t="n"/>
+      <c r="K32" s="85" t="n"/>
+    </row>
+    <row r="33" customFormat="1" s="84">
+      <c r="A33" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B33" s="72" t="n"/>
+      <c r="C33" s="78" t="n"/>
+      <c r="D33" s="79" t="n"/>
+      <c r="E33" s="78" t="n"/>
+      <c r="F33" s="186" t="n"/>
+      <c r="G33" s="187" t="n"/>
+      <c r="H33" s="188" t="n"/>
+      <c r="I33" s="186">
+        <f>SUM(D33+F33+(G33*5.5)+H33)</f>
+        <v/>
+      </c>
+      <c r="J33" s="189" t="n"/>
+      <c r="K33" s="85" t="n"/>
+    </row>
+    <row r="34" ht="14.45" customFormat="1" customHeight="1" s="84" thickBot="1">
+      <c r="A34" s="193" t="n"/>
+      <c r="B34" s="194" t="n"/>
+      <c r="C34" s="194" t="n"/>
+      <c r="D34" s="194" t="n"/>
+      <c r="E34" s="194" t="n"/>
+      <c r="F34" s="194" t="n"/>
+      <c r="G34" s="194" t="n"/>
+      <c r="H34" s="194" t="n"/>
+      <c r="I34" s="195" t="n"/>
+      <c r="K34" s="85" t="n"/>
+    </row>
+    <row r="35" hidden="1" ht="21.6" customFormat="1" customHeight="1" s="84">
+      <c r="A35" s="112" t="n">
         <v>4</v>
       </c>
-      <c r="B28" s="196" t="inlineStr">
+      <c r="B35" s="196" t="inlineStr">
         <is>
           <t>Service cost (PAH,HAW)</t>
         </is>
       </c>
-      <c r="C28" s="197" t="n"/>
-      <c r="D28" s="198" t="n"/>
-      <c r="E28" s="199" t="n"/>
-      <c r="F28" s="117" t="n"/>
-      <c r="G28" s="118">
-        <f>F28&amp;"km"</f>
+      <c r="C35" s="197" t="n"/>
+      <c r="D35" s="198" t="n"/>
+      <c r="E35" s="199" t="n"/>
+      <c r="F35" s="117" t="n"/>
+      <c r="G35" s="118">
+        <f>F35&amp;"km"</f>
         <v/>
       </c>
-      <c r="H28" s="117" t="n"/>
-      <c r="I28" s="200">
-        <f>SUM(E28+(F28*5.5)+H28)</f>
+      <c r="H35" s="117" t="n"/>
+      <c r="I35" s="200">
+        <f>SUM(E35+(F35*5.5)+H35)</f>
         <v/>
       </c>
-      <c r="K28" s="85" t="n"/>
-    </row>
-    <row r="29" ht="20.45" customFormat="1" customHeight="1" s="84">
-      <c r="A29" s="124" t="n">
+      <c r="K35" s="85" t="n"/>
+    </row>
+    <row r="36" ht="20.45" customFormat="1" customHeight="1" s="84">
+      <c r="A36" s="124" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="201" t="inlineStr">
+      <c r="B36" s="201" t="inlineStr">
         <is>
           <t>Sampling</t>
         </is>
       </c>
-      <c r="C29" s="173" t="n"/>
-      <c r="D29" s="173" t="n"/>
-      <c r="E29" s="174" t="n"/>
-      <c r="F29" s="202" t="n"/>
-      <c r="G29" s="203" t="n"/>
-      <c r="H29" s="204" t="n"/>
-      <c r="I29" s="205">
-        <f>SUM(F29+(G29*5.5)+H29)</f>
+      <c r="C36" s="173" t="n"/>
+      <c r="D36" s="173" t="n"/>
+      <c r="E36" s="174" t="n"/>
+      <c r="F36" s="202" t="n"/>
+      <c r="G36" s="203" t="n"/>
+      <c r="H36" s="204" t="n"/>
+      <c r="I36" s="205">
+        <f>SUM(F36+(G36*5.5)+H36)</f>
         <v/>
       </c>
-      <c r="K29" s="85" t="n"/>
-    </row>
-    <row r="30" ht="19.35" customFormat="1" customHeight="1" s="84" thickBot="1">
-      <c r="A30" s="108" t="n">
+      <c r="K36" s="85" t="n"/>
+    </row>
+    <row r="37" ht="19.35" customFormat="1" customHeight="1" s="84" thickBot="1">
+      <c r="A37" s="108" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="206" t="inlineStr">
+      <c r="B37" s="206" t="inlineStr">
         <is>
           <t>Audit verification</t>
         </is>
       </c>
-      <c r="C30" s="180" t="n"/>
-      <c r="D30" s="180" t="n"/>
-      <c r="E30" s="181" t="n"/>
-      <c r="F30" s="207" t="n"/>
-      <c r="G30" s="208" t="n"/>
-      <c r="H30" s="209" t="n"/>
-      <c r="I30" s="210">
-        <f>SUM(F30+(G30*5.5)+H30)</f>
+      <c r="C37" s="180" t="n"/>
+      <c r="D37" s="180" t="n"/>
+      <c r="E37" s="181" t="n"/>
+      <c r="F37" s="207" t="n"/>
+      <c r="G37" s="208" t="n"/>
+      <c r="H37" s="209" t="n"/>
+      <c r="I37" s="210">
+        <f>SUM(F37+(G37*5.5)+H37)</f>
         <v/>
       </c>
-      <c r="K30" s="85" t="n"/>
-    </row>
-    <row r="31" ht="30" customFormat="1" customHeight="1" s="84" thickBot="1">
-      <c r="A31" s="211" t="inlineStr">
+      <c r="K37" s="85" t="n"/>
+    </row>
+    <row r="38" ht="30" customFormat="1" customHeight="1" s="84" thickBot="1">
+      <c r="A38" s="211" t="inlineStr">
         <is>
           <t>Sub - total</t>
-        </is>
-      </c>
-      <c r="B31" s="194" t="n"/>
-      <c r="C31" s="194" t="n"/>
-      <c r="D31" s="194" t="n"/>
-      <c r="E31" s="194" t="n"/>
-      <c r="F31" s="194" t="n"/>
-      <c r="G31" s="194" t="n"/>
-      <c r="H31" s="212" t="n"/>
-      <c r="I31" s="213">
-        <f>SUM(I22:I30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="85" t="n"/>
-    </row>
-    <row r="32" hidden="1" ht="30" customFormat="1" customHeight="1" s="84">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="214" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="215" t="n"/>
-      <c r="K32" s="85" t="n"/>
-    </row>
-    <row r="33" hidden="1" ht="30" customFormat="1" customHeight="1" s="84">
-      <c r="A33" s="112" t="n"/>
-      <c r="B33" s="139" t="n"/>
-      <c r="C33" s="140" t="n"/>
-      <c r="D33" s="141" t="n"/>
-      <c r="E33" s="216" t="n"/>
-      <c r="F33" s="143" t="n"/>
-      <c r="G33" s="143" t="n"/>
-      <c r="H33" s="144" t="n"/>
-      <c r="I33" s="217" t="n"/>
-      <c r="K33" s="85" t="n"/>
-    </row>
-    <row r="34" ht="16.5" customFormat="1" customHeight="1" s="218">
-      <c r="A34" s="242" t="inlineStr">
-        <is>
-          <t>Conducting an audit verification &amp; sampling enables us to provide you with a discount.</t>
-        </is>
-      </c>
-      <c r="B34" s="170" t="n"/>
-      <c r="C34" s="220" t="inlineStr">
-        <is>
-          <t>Discounted</t>
-        </is>
-      </c>
-      <c r="D34" s="220" t="n"/>
-      <c r="E34" s="174" t="n"/>
-      <c r="F34" s="221" t="n"/>
-      <c r="G34" s="222" t="n"/>
-      <c r="H34" s="223" t="n"/>
-      <c r="I34" s="224">
-        <f>SUM(D34+F34+(G34*5.5)+H34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="189" t="n"/>
-      <c r="K34" s="189" t="n"/>
-      <c r="L34" s="189" t="n"/>
-      <c r="M34" s="189" t="n"/>
-      <c r="N34" s="189" t="n"/>
-      <c r="O34" s="189" t="n"/>
-      <c r="P34" s="189" t="n"/>
-      <c r="Q34" s="189" t="n"/>
-      <c r="R34" s="189" t="n"/>
-      <c r="S34" s="189" t="n"/>
-      <c r="T34" s="189" t="n"/>
-      <c r="U34" s="189" t="n"/>
-      <c r="V34" s="189" t="n"/>
-      <c r="W34" s="189" t="n"/>
-      <c r="X34" s="189" t="n"/>
-      <c r="Y34" s="189" t="n"/>
-      <c r="Z34" s="189" t="n"/>
-      <c r="AA34" s="189" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="22" t="n"/>
-      <c r="C35" s="225" t="inlineStr">
-        <is>
-          <t>Discounted</t>
-        </is>
-      </c>
-      <c r="D35" s="225" t="n"/>
-      <c r="E35" s="176" t="n"/>
-      <c r="F35" s="226" t="n"/>
-      <c r="G35" s="227" t="n"/>
-      <c r="H35" s="226" t="n"/>
-      <c r="I35" s="228">
-        <f>SUM(D35+F35+(G35*5.5)+H35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="n"/>
-      <c r="C36" s="225" t="inlineStr">
-        <is>
-          <t>Discounted</t>
-        </is>
-      </c>
-      <c r="D36" s="225" t="n"/>
-      <c r="E36" s="176" t="n"/>
-      <c r="F36" s="226" t="n"/>
-      <c r="G36" s="227" t="n"/>
-      <c r="H36" s="226" t="n"/>
-      <c r="I36" s="228">
-        <f>SUM(D36+F36+(G36*5.5)+H36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" s="95" thickBot="1">
-      <c r="A37" s="23" t="n"/>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="229" t="inlineStr">
-        <is>
-          <t>Discounted</t>
-        </is>
-      </c>
-      <c r="D37" s="229" t="n"/>
-      <c r="E37" s="181" t="n"/>
-      <c r="F37" s="230" t="n"/>
-      <c r="G37" s="231" t="n"/>
-      <c r="H37" s="230" t="n"/>
-      <c r="I37" s="232">
-        <f>SUM(D37+F37+(G37*5.5)+H37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22.5" customFormat="1" customHeight="1" s="5">
-      <c r="A38" s="233" t="inlineStr">
-        <is>
-          <t>Discount provided</t>
         </is>
       </c>
       <c r="B38" s="194" t="n"/>
@@ -2883,115 +2874,250 @@
       <c r="F38" s="194" t="n"/>
       <c r="G38" s="194" t="n"/>
       <c r="H38" s="212" t="n"/>
-      <c r="I38" s="234">
-        <f>SUM(I34:I37)</f>
+      <c r="I38" s="213">
+        <f>SUM(I22:I37)</f>
         <v/>
       </c>
-    </row>
-    <row r="39" ht="19.5" customFormat="1" customHeight="1" s="5" thickBot="1">
-      <c r="A39" s="235" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> TOTAL Excl 15% VAT</t>
-        </is>
-      </c>
-      <c r="B39" s="180" t="n"/>
-      <c r="C39" s="180" t="n"/>
-      <c r="D39" s="180" t="n"/>
-      <c r="E39" s="180" t="n"/>
-      <c r="F39" s="180" t="n"/>
-      <c r="G39" s="180" t="n"/>
-      <c r="H39" s="236" t="n"/>
-      <c r="I39" s="237">
-        <f>I31+I38</f>
+      <c r="K38" s="85" t="n"/>
+    </row>
+    <row r="39" hidden="1" ht="30" customFormat="1" customHeight="1" s="84">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="214" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="215" t="n"/>
+      <c r="K39" s="85" t="n"/>
+    </row>
+    <row r="40" hidden="1" ht="30" customFormat="1" customHeight="1" s="84">
+      <c r="A40" s="112" t="n"/>
+      <c r="B40" s="139" t="n"/>
+      <c r="C40" s="140" t="n"/>
+      <c r="D40" s="141" t="n"/>
+      <c r="E40" s="216" t="n"/>
+      <c r="F40" s="143" t="n"/>
+      <c r="G40" s="143" t="n"/>
+      <c r="H40" s="144" t="n"/>
+      <c r="I40" s="217" t="n"/>
+      <c r="K40" s="85" t="n"/>
+    </row>
+    <row r="41" ht="16.5" customFormat="1" customHeight="1" s="218">
+      <c r="A41" s="242" t="inlineStr">
+        <is>
+          <t>Conducting an audit verification &amp; sampling enables us to provide you with a discount.</t>
+        </is>
+      </c>
+      <c r="B41" s="170" t="n"/>
+      <c r="C41" s="220" t="inlineStr">
+        <is>
+          <t>Discounted</t>
+        </is>
+      </c>
+      <c r="D41" s="220" t="n"/>
+      <c r="E41" s="174" t="n"/>
+      <c r="F41" s="221" t="n"/>
+      <c r="G41" s="222" t="n"/>
+      <c r="H41" s="223" t="n"/>
+      <c r="I41" s="224">
+        <f>SUM(F41+(G41*5.5)+H41)</f>
         <v/>
       </c>
-    </row>
-    <row r="40" ht="23.45" customHeight="1" s="95">
-      <c r="A40" s="238" t="inlineStr">
-        <is>
-          <t>For acceptance of the quote, please sign below and email back the signed copy</t>
-        </is>
-      </c>
-      <c r="B40" s="170" t="n"/>
-      <c r="C40" s="170" t="n"/>
-      <c r="D40" s="170" t="n"/>
-      <c r="E40" s="170" t="n"/>
-      <c r="F40" s="170" t="n"/>
-      <c r="G40" s="170" t="n"/>
-      <c r="H40" s="170" t="n"/>
-      <c r="I40" s="239" t="n"/>
-    </row>
-    <row r="41" ht="26.1" customHeight="1" s="95">
-      <c r="A41" s="22" t="n"/>
-      <c r="B41" s="70" t="n"/>
-      <c r="C41" s="194" t="n"/>
-      <c r="E41" s="168" t="n"/>
-      <c r="H41" s="71" t="n"/>
-      <c r="I41" s="195" t="n"/>
+      <c r="J41" s="189" t="n"/>
+      <c r="K41" s="189" t="n"/>
+      <c r="L41" s="189" t="n"/>
+      <c r="M41" s="189" t="n"/>
+      <c r="N41" s="189" t="n"/>
+      <c r="O41" s="189" t="n"/>
+      <c r="P41" s="189" t="n"/>
+      <c r="Q41" s="189" t="n"/>
+      <c r="R41" s="189" t="n"/>
+      <c r="S41" s="189" t="n"/>
+      <c r="T41" s="189" t="n"/>
+      <c r="U41" s="189" t="n"/>
+      <c r="V41" s="189" t="n"/>
+      <c r="W41" s="189" t="n"/>
+      <c r="X41" s="189" t="n"/>
+      <c r="Y41" s="189" t="n"/>
+      <c r="Z41" s="189" t="n"/>
+      <c r="AA41" s="189" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="22" t="n"/>
-      <c r="B42" s="97" t="inlineStr">
+      <c r="C42" s="225" t="inlineStr">
+        <is>
+          <t>Discounted</t>
+        </is>
+      </c>
+      <c r="D42" s="225" t="n"/>
+      <c r="E42" s="176" t="n"/>
+      <c r="F42" s="226" t="n"/>
+      <c r="G42" s="227" t="n"/>
+      <c r="H42" s="226" t="n"/>
+      <c r="I42" s="228">
+        <f>SUM(F42+(G42*5.5)+H42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n"/>
+      <c r="C43" s="225" t="inlineStr">
+        <is>
+          <t>Discounted</t>
+        </is>
+      </c>
+      <c r="D43" s="225" t="n"/>
+      <c r="E43" s="176" t="n"/>
+      <c r="F43" s="226" t="n"/>
+      <c r="G43" s="227" t="n"/>
+      <c r="H43" s="226" t="n"/>
+      <c r="I43" s="228">
+        <f>SUM(F43+(G43*5.5)+H43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="95" thickBot="1">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="229" t="inlineStr">
+        <is>
+          <t>Discounted</t>
+        </is>
+      </c>
+      <c r="D44" s="229" t="n"/>
+      <c r="E44" s="181" t="n"/>
+      <c r="F44" s="230" t="n"/>
+      <c r="G44" s="231" t="n"/>
+      <c r="H44" s="230" t="n"/>
+      <c r="I44" s="232">
+        <f>SUM(F44+(G44*5.5)+H44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customFormat="1" customHeight="1" s="5">
+      <c r="A45" s="233" t="inlineStr">
+        <is>
+          <t>Discount provided</t>
+        </is>
+      </c>
+      <c r="B45" s="194" t="n"/>
+      <c r="C45" s="194" t="n"/>
+      <c r="D45" s="194" t="n"/>
+      <c r="E45" s="194" t="n"/>
+      <c r="F45" s="194" t="n"/>
+      <c r="G45" s="194" t="n"/>
+      <c r="H45" s="212" t="n"/>
+      <c r="I45" s="234">
+        <f>SUM(I41:I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="19.5" customFormat="1" customHeight="1" s="5" thickBot="1">
+      <c r="A46" s="235" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> TOTAL Excl 15% VAT</t>
+        </is>
+      </c>
+      <c r="B46" s="180" t="n"/>
+      <c r="C46" s="180" t="n"/>
+      <c r="D46" s="180" t="n"/>
+      <c r="E46" s="180" t="n"/>
+      <c r="F46" s="180" t="n"/>
+      <c r="G46" s="180" t="n"/>
+      <c r="H46" s="236" t="n"/>
+      <c r="I46" s="237">
+        <f>I38+I45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="23.45" customHeight="1" s="95">
+      <c r="A47" s="238" t="inlineStr">
+        <is>
+          <t>For acceptance of the quote, please sign below and email back the signed copy</t>
+        </is>
+      </c>
+      <c r="B47" s="170" t="n"/>
+      <c r="C47" s="170" t="n"/>
+      <c r="D47" s="170" t="n"/>
+      <c r="E47" s="170" t="n"/>
+      <c r="F47" s="170" t="n"/>
+      <c r="G47" s="170" t="n"/>
+      <c r="H47" s="170" t="n"/>
+      <c r="I47" s="239" t="n"/>
+    </row>
+    <row r="48" ht="26.1" customHeight="1" s="95">
+      <c r="A48" s="22" t="n"/>
+      <c r="B48" s="70" t="n"/>
+      <c r="C48" s="194" t="n"/>
+      <c r="E48" s="168" t="n"/>
+      <c r="H48" s="71" t="n"/>
+      <c r="I48" s="195" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n"/>
+      <c r="B49" s="97" t="inlineStr">
         <is>
           <t>Client</t>
         </is>
       </c>
-      <c r="C42" s="97" t="n"/>
-      <c r="E42" s="168" t="n"/>
-      <c r="H42" s="69" t="inlineStr">
+      <c r="C49" s="97" t="n"/>
+      <c r="E49" s="168" t="n"/>
+      <c r="H49" s="69" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="I42" s="240" t="n"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" s="95" thickBot="1">
-      <c r="A43" s="23" t="n"/>
-      <c r="B43" s="1" t="n"/>
-      <c r="C43" s="1" t="n"/>
-      <c r="D43" s="1" t="n"/>
-      <c r="E43" s="169" t="n"/>
-      <c r="F43" s="1" t="n"/>
-      <c r="G43" s="1" t="n"/>
-      <c r="H43" s="1" t="n"/>
-      <c r="I43" s="241" t="n"/>
-    </row>
-    <row r="44" ht="52.5" customHeight="1" s="95">
-      <c r="A44" s="67" t="inlineStr">
+      <c r="I49" s="240" t="n"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" s="95" thickBot="1">
+      <c r="A50" s="23" t="n"/>
+      <c r="B50" s="1" t="n"/>
+      <c r="C50" s="1" t="n"/>
+      <c r="D50" s="1" t="n"/>
+      <c r="E50" s="169" t="n"/>
+      <c r="F50" s="1" t="n"/>
+      <c r="G50" s="1" t="n"/>
+      <c r="H50" s="1" t="n"/>
+      <c r="I50" s="241" t="n"/>
+    </row>
+    <row r="51" ht="52.5" customHeight="1" s="95">
+      <c r="A51" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">General Manager : Dr GC Neethling
  Red Meat Abattoir Association                                                                     Abattoir Skills Training
 </t>
         </is>
       </c>
-      <c r="B44" s="170" t="n"/>
-      <c r="C44" s="170" t="n"/>
-      <c r="D44" s="170" t="n"/>
-      <c r="E44" s="170" t="n"/>
-      <c r="F44" s="170" t="n"/>
-      <c r="G44" s="170" t="n"/>
-      <c r="H44" s="170" t="n"/>
-      <c r="I44" s="170" t="n"/>
+      <c r="B51" s="170" t="n"/>
+      <c r="C51" s="170" t="n"/>
+      <c r="D51" s="170" t="n"/>
+      <c r="E51" s="170" t="n"/>
+      <c r="F51" s="170" t="n"/>
+      <c r="G51" s="170" t="n"/>
+      <c r="H51" s="170" t="n"/>
+      <c r="I51" s="170" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="55">
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D2:I2"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="D13:I13"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="D17:I17"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D16:I16"/>
-    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="D43:E43"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A14:C14"/>
@@ -3009,27 +3135,27 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A34:B37"/>
+    <mergeCell ref="A41:B44"/>
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="A44:I44"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="A47:I47"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D19:I19"/>
     <mergeCell ref="D10:I10"/>
     <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D42:E42"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId1"/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -1692,12 +1692,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1">
-          <clrChange>
-            <clrFrom/>
-            <clrTo/>
-          </clrChange>
-        </a:blip>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -1744,12 +1739,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <clrChange>
-            <clrFrom/>
-            <clrTo/>
-          </clrChange>
-        </a:blip>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -1675,13 +1675,13 @@
     <from>
       <col>0</col>
       <colOff>97291</colOff>
-      <row>43</row>
+      <row>50</row>
       <rowOff>46377</rowOff>
     </from>
     <to>
       <col>1</col>
       <colOff>297656</colOff>
-      <row>43</row>
+      <row>50</row>
       <rowOff>639103</rowOff>
     </to>
     <pic>
@@ -1806,13 +1806,13 @@
     <from>
       <col>8</col>
       <colOff>98880</colOff>
-      <row>43</row>
+      <row>50</row>
       <rowOff>32945</rowOff>
     </from>
     <to>
       <col>9</col>
       <colOff>2211</colOff>
-      <row>43</row>
+      <row>50</row>
       <rowOff>659475</rowOff>
     </to>
     <pic>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -2773,7 +2773,7 @@
       <c r="J33" s="189" t="n"/>
       <c r="K33" s="85" t="n"/>
     </row>
-    <row r="34" ht="14.45" customFormat="1" customHeight="1" s="84" thickBot="1">
+    <row r="34" ht="14.45" customFormat="1" customHeight="1" s="84">
       <c r="A34" s="193" t="n"/>
       <c r="B34" s="194" t="n"/>
       <c r="C34" s="194" t="n"/>
@@ -2810,8 +2810,10 @@
       <c r="K35" s="85" t="n"/>
     </row>
     <row r="36" ht="20.45" customFormat="1" customHeight="1" s="84">
-      <c r="A36" s="124" t="n">
-        <v>4</v>
+      <c r="A36" s="124" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="B36" s="201" t="inlineStr">
         <is>
@@ -2831,8 +2833,10 @@
       <c r="K36" s="85" t="n"/>
     </row>
     <row r="37" ht="19.35" customFormat="1" customHeight="1" s="84" thickBot="1">
-      <c r="A37" s="108" t="n">
-        <v>5</v>
+      <c r="A37" s="108" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
       </c>
       <c r="B37" s="206" t="inlineStr">
         <is>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -996,7 +996,7 @@
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1656,6 +1656,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2581,7 +2587,7 @@
       </c>
       <c r="B23" s="72" t="n"/>
       <c r="C23" s="78" t="n"/>
-      <c r="D23" s="79" t="n"/>
+      <c r="D23" s="243" t="n"/>
       <c r="E23" s="78" t="n"/>
       <c r="F23" s="186" t="n"/>
       <c r="G23" s="187" t="n"/>
@@ -2599,7 +2605,7 @@
       </c>
       <c r="B24" s="72" t="n"/>
       <c r="C24" s="78" t="n"/>
-      <c r="D24" s="79" t="n"/>
+      <c r="D24" s="243" t="n"/>
       <c r="E24" s="78" t="n"/>
       <c r="F24" s="186" t="n"/>
       <c r="G24" s="187" t="n"/>
@@ -2617,7 +2623,7 @@
       </c>
       <c r="B25" s="72" t="n"/>
       <c r="C25" s="78" t="n"/>
-      <c r="D25" s="79" t="n"/>
+      <c r="D25" s="243" t="n"/>
       <c r="E25" s="78" t="n"/>
       <c r="F25" s="186" t="n"/>
       <c r="G25" s="187" t="n"/>
@@ -2653,7 +2659,7 @@
       </c>
       <c r="B27" s="72" t="n"/>
       <c r="C27" s="78" t="n"/>
-      <c r="D27" s="79" t="n"/>
+      <c r="D27" s="243" t="n"/>
       <c r="E27" s="78" t="n"/>
       <c r="F27" s="186" t="n"/>
       <c r="G27" s="187" t="n"/>
@@ -2671,7 +2677,7 @@
       </c>
       <c r="B28" s="72" t="n"/>
       <c r="C28" s="78" t="n"/>
-      <c r="D28" s="79" t="n"/>
+      <c r="D28" s="243" t="n"/>
       <c r="E28" s="78" t="n"/>
       <c r="F28" s="186" t="n"/>
       <c r="G28" s="187" t="n"/>
@@ -2689,7 +2695,7 @@
       </c>
       <c r="B29" s="72" t="n"/>
       <c r="C29" s="78" t="n"/>
-      <c r="D29" s="79" t="n"/>
+      <c r="D29" s="243" t="n"/>
       <c r="E29" s="78" t="n"/>
       <c r="F29" s="186" t="n"/>
       <c r="G29" s="187" t="n"/>
@@ -2707,7 +2713,7 @@
       </c>
       <c r="B30" s="72" t="n"/>
       <c r="C30" s="78" t="n"/>
-      <c r="D30" s="79" t="n"/>
+      <c r="D30" s="243" t="n"/>
       <c r="E30" s="78" t="n"/>
       <c r="F30" s="186" t="n"/>
       <c r="G30" s="187" t="n"/>
@@ -2725,7 +2731,7 @@
       </c>
       <c r="B31" s="72" t="n"/>
       <c r="C31" s="78" t="n"/>
-      <c r="D31" s="79" t="n"/>
+      <c r="D31" s="243" t="n"/>
       <c r="E31" s="78" t="n"/>
       <c r="F31" s="186" t="n"/>
       <c r="G31" s="187" t="n"/>
@@ -2743,7 +2749,7 @@
       </c>
       <c r="B32" s="72" t="n"/>
       <c r="C32" s="78" t="n"/>
-      <c r="D32" s="79" t="n"/>
+      <c r="D32" s="243" t="n"/>
       <c r="E32" s="78" t="n"/>
       <c r="F32" s="186" t="n"/>
       <c r="G32" s="187" t="n"/>
@@ -2761,7 +2767,7 @@
       </c>
       <c r="B33" s="72" t="n"/>
       <c r="C33" s="78" t="n"/>
-      <c r="D33" s="79" t="n"/>
+      <c r="D33" s="243" t="n"/>
       <c r="E33" s="78" t="n"/>
       <c r="F33" s="186" t="n"/>
       <c r="G33" s="187" t="n"/>
@@ -2914,7 +2920,7 @@
       <c r="E41" s="174" t="n"/>
       <c r="F41" s="221" t="n"/>
       <c r="G41" s="222" t="n"/>
-      <c r="H41" s="223" t="n"/>
+      <c r="H41" s="221" t="n"/>
       <c r="I41" s="224">
         <f>SUM(F41+(G41*5.5)+H41)</f>
         <v/>

--- a/Quotation Template.xlsx
+++ b/Quotation Template.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="168" formatCode="0\ &quot;km&quot;"/>
     <numFmt numFmtId="169" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -250,6 +250,13 @@
       <color rgb="FFFF0000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -996,7 +1003,7 @@
     </xf>
     <xf numFmtId="169" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1662,6 +1669,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="28" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="31" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2269,7 +2285,7 @@
       </c>
       <c r="B7" s="175" t="n"/>
       <c r="C7" s="176" t="n"/>
-      <c r="D7" s="178" t="inlineStr">
+      <c r="D7" s="246" t="inlineStr">
         <is>
           <t>4920255173</t>
         </is>
@@ -2278,7 +2294,7 @@
       <c r="F7" s="175" t="n"/>
       <c r="G7" s="175" t="n"/>
       <c r="H7" s="175" t="n"/>
-      <c r="I7" s="179" t="n"/>
+      <c r="I7" s="176" t="n"/>
     </row>
     <row r="8" hidden="1" ht="14.45" customHeight="1" s="95">
       <c r="A8" s="34" t="inlineStr">
@@ -2635,18 +2651,18 @@
       <c r="J25" s="189" t="n"/>
       <c r="K25" s="85" t="n"/>
     </row>
-    <row r="26" customFormat="1" s="84" thickBot="1">
-      <c r="A26" s="108" t="n">
+    <row r="26" customFormat="1" s="84">
+      <c r="A26" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B26" s="109" t="n"/>
-      <c r="C26" s="80" t="n"/>
-      <c r="D26" s="190" t="n"/>
-      <c r="E26" s="80" t="n"/>
-      <c r="F26" s="190" t="n"/>
-      <c r="G26" s="191" t="n"/>
-      <c r="H26" s="192" t="n"/>
-      <c r="I26" s="190">
+      <c r="B26" s="72" t="n"/>
+      <c r="C26" s="78" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="78" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="98" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="27">
         <f>SUM(D26+F26+(G26*5.5)+H26)</f>
         <v/>
       </c>
@@ -2780,7 +2796,7 @@
       <c r="K33" s="85" t="n"/>
     </row>
     <row r="34" ht="14.45" customFormat="1" customHeight="1" s="84">
-      <c r="A34" s="193" t="n"/>
+      <c r="A34" s="247" t="n"/>
       <c r="B34" s="194" t="n"/>
       <c r="C34" s="194" t="n"/>
       <c r="D34" s="194" t="n"/>
@@ -2791,30 +2807,7 @@
       <c r="I34" s="195" t="n"/>
       <c r="K34" s="85" t="n"/>
     </row>
-    <row r="35" hidden="1" ht="21.6" customFormat="1" customHeight="1" s="84">
-      <c r="A35" s="112" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="196" t="inlineStr">
-        <is>
-          <t>Service cost (PAH,HAW)</t>
-        </is>
-      </c>
-      <c r="C35" s="197" t="n"/>
-      <c r="D35" s="198" t="n"/>
-      <c r="E35" s="199" t="n"/>
-      <c r="F35" s="117" t="n"/>
-      <c r="G35" s="118">
-        <f>F35&amp;"km"</f>
-        <v/>
-      </c>
-      <c r="H35" s="117" t="n"/>
-      <c r="I35" s="200">
-        <f>SUM(E35+(F35*5.5)+H35)</f>
-        <v/>
-      </c>
-      <c r="K35" s="85" t="n"/>
-    </row>
+    <row r="35" hidden="1" ht="21.6" customFormat="1" customHeight="1" s="84"/>
     <row r="36" ht="20.45" customFormat="1" customHeight="1" s="84">
       <c r="A36" s="124" t="inlineStr">
         <is>
@@ -3100,7 +3093,7 @@
       <c r="I51" s="170" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="54">
     <mergeCell ref="D11:I11"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="A46:H46"/>
@@ -3117,7 +3110,6 @@
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="D7:I7"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="B35:D35"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="A14:C14"/>
